--- a/research/traditional_assets/database/data/ivory_coast/ivory_coast_chemical_specialty.xlsx
+++ b/research/traditional_assets/database/data/ivory_coast/ivory_coast_chemical_specialty.xlsx
@@ -633,10 +633,10 @@
         <v>0</v>
       </c>
       <c r="X2">
-        <v>0.09369152194077801</v>
+        <v>0.1629033087838683</v>
       </c>
       <c r="AB2">
-        <v>0.09369152194077801</v>
+        <v>0.1629033087838683</v>
       </c>
       <c r="AD2">
         <v>0</v>
@@ -737,10 +737,10 @@
         <v>0</v>
       </c>
       <c r="X3">
-        <v>0.09369152194077801</v>
+        <v>0.1629033087838683</v>
       </c>
       <c r="AB3">
-        <v>0.09369152194077801</v>
+        <v>0.1629033087838683</v>
       </c>
       <c r="AD3">
         <v>0</v>
